--- a/data/trans_orig/IP07A06-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07A06-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse triste en 2007 (tasa de respuesta: 99,7%)</t>
+          <t>Menores según la frecuencia de sentirse triste, percibida por el adulto en 2007 (tasa de respuesta: 99,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4919</t>
+          <t>4792</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3401</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>648</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5378</t>
+          <t>5466</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3639</t>
+          <t>3657</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3289</t>
+          <t>3651</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4980</t>
+          <t>4305</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10127</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22467</t>
+          <t>21828</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15134</t>
+          <t>14376</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29076</t>
+          <t>28193</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>27799</t>
+          <t>28690</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>46347</t>
+          <t>47000</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,47%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36875</t>
+          <t>37586</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54503</t>
+          <t>54499</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43515</t>
+          <t>43769</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62041</t>
+          <t>61573</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>86203</t>
+          <t>85794</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>110766</t>
+          <t>111080</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>41,28%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>54570</t>
+          <t>54669</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>72945</t>
+          <t>73278</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>56549</t>
+          <t>56691</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>75437</t>
+          <t>75963</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>117288</t>
+          <t>116589</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>144039</t>
+          <t>144526</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>43,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>53,71%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>655</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5953</t>
+          <t>5890</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3696</t>
+          <t>3353</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>682</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6577</t>
+          <t>6765</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>2082</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9725</t>
+          <t>9898</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4091</t>
+          <t>4455</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2186</t>
+          <t>2617</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10102</t>
+          <t>10382</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25990</t>
+          <t>26087</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>42815</t>
+          <t>42207</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>19048</t>
+          <t>18907</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>35604</t>
+          <t>35145</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>49678</t>
+          <t>48239</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>72224</t>
+          <t>72314</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,16%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48466</t>
+          <t>49004</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>69818</t>
+          <t>68765</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47237</t>
+          <t>47809</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67435</t>
+          <t>68803</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>100936</t>
+          <t>101847</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>130215</t>
+          <t>129065</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,41%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>84097</t>
+          <t>84400</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>105802</t>
+          <t>106203</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>54,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>107434</t>
+          <t>107427</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>130046</t>
+          <t>130030</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,65%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>198924</t>
+          <t>198407</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>231190</t>
+          <t>229851</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>57,73%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1358</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7596</t>
+          <t>8147</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4413</t>
+          <t>3992</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2089</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9389</t>
+          <t>9403</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2631</t>
+          <t>2677</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10492</t>
+          <t>10767</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4091</t>
+          <t>4775</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3383</t>
+          <t>3491</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>12107</t>
+          <t>12111</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>39075</t>
+          <t>38552</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>60542</t>
+          <t>60319</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>38047</t>
+          <t>37718</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>58118</t>
+          <t>58730</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>82495</t>
+          <t>82887</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>112019</t>
+          <t>113846</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>17,06%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>90872</t>
+          <t>91428</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>118674</t>
+          <t>118506</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>96718</t>
+          <t>97381</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>124543</t>
+          <t>124045</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>197437</t>
+          <t>194048</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>235025</t>
+          <t>234489</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,14%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>144076</t>
+          <t>144292</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>173385</t>
+          <t>172651</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>170498</t>
+          <t>171628</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>201348</t>
+          <t>200630</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>58,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>324615</t>
+          <t>324441</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>364313</t>
+          <t>367843</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>55,13%</t>
         </is>
       </c>
     </row>
@@ -2814,7 +2814,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse triste en 2012 (tasa de respuesta: 98,12%)</t>
+          <t>Menores según la frecuencia de sentirse triste, percibida por el adulto en 2012 (tasa de respuesta: 98,12%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9244</t>
+          <t>9313</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4930</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2680</t>
+          <t>2752</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>10493</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7993</t>
+          <t>7658</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>572</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>5310</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2943</t>
+          <t>3120</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10939</t>
+          <t>11231</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13220</t>
+          <t>13281</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27294</t>
+          <t>27004</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22724</t>
+          <t>22977</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>40249</t>
+          <t>39505</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>40658</t>
+          <t>40998</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>61988</t>
+          <t>62023</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,87%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40327</t>
+          <t>40130</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59982</t>
+          <t>60483</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33921</t>
+          <t>34146</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51920</t>
+          <t>52883</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>78097</t>
+          <t>79814</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>104691</t>
+          <t>106194</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>34,02%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>68789</t>
+          <t>68323</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>89092</t>
+          <t>88776</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>70011</t>
+          <t>69983</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>91091</t>
+          <t>90052</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>57,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>144332</t>
+          <t>142629</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>173601</t>
+          <t>172799</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>55,35%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>585</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5095</t>
+          <t>4969</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>760</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6794</t>
+          <t>6774</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2068</t>
+          <t>1924</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8932</t>
+          <t>9603</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1219</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7210</t>
+          <t>8366</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1194</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7417</t>
+          <t>7839</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3743</t>
+          <t>3651</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12739</t>
+          <t>12233</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26588</t>
+          <t>26381</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>44895</t>
+          <t>44769</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>25880</t>
+          <t>25060</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>42945</t>
+          <t>41527</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>56929</t>
+          <t>57441</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>82099</t>
+          <t>81572</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,83%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47262</t>
+          <t>48525</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>67280</t>
+          <t>68035</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>49781</t>
+          <t>49459</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69600</t>
+          <t>69780</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>103258</t>
+          <t>102914</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>131666</t>
+          <t>131777</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>38,5%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>58780</t>
+          <t>56966</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>78560</t>
+          <t>77332</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>67132</t>
+          <t>67167</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>88275</t>
+          <t>88358</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>128193</t>
+          <t>129282</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>159616</t>
+          <t>159739</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>46,67%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2688</t>
+          <t>2717</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11219</t>
+          <t>10650</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8192</t>
+          <t>8639</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5616</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16123</t>
+          <t>15719</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3811</t>
+          <t>3480</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12268</t>
+          <t>12410</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2700</t>
+          <t>2999</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11167</t>
+          <t>10497</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>7991</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>19338</t>
+          <t>19401</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>44411</t>
+          <t>44486</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>67642</t>
+          <t>67694</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>52652</t>
+          <t>53180</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>74825</t>
+          <t>76714</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>102382</t>
+          <t>103931</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>137366</t>
+          <t>136977</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,93%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>94657</t>
+          <t>94143</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>121373</t>
+          <t>121109</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>87374</t>
+          <t>89127</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>115139</t>
+          <t>115975</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>191556</t>
+          <t>189301</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>228984</t>
+          <t>230097</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>35,16%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>130960</t>
+          <t>131178</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>160358</t>
+          <t>160789</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>143328</t>
+          <t>142362</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>172865</t>
+          <t>171512</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>51,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>284481</t>
+          <t>281043</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>325194</t>
+          <t>322562</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>49,28%</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5090,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse triste en 2016 (tasa de respuesta: 99,02%)</t>
+          <t>Menores según la frecuencia de sentirse triste, percibida por el adulto en 2016 (tasa de respuesta: 99,02%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3624</t>
+          <t>3650</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5026</t>
+          <t>5687</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>668</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5671</t>
+          <t>5795</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5375,7 +5375,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -5398,12 +5398,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>1133</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7285</t>
+          <t>6746</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5413,12 +5413,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5433,12 +5433,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>2780</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11280</t>
+          <t>10578</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5448,12 +5448,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5468,12 +5468,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5333</t>
+          <t>5433</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15619</t>
+          <t>15136</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5483,12 +5483,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -5511,12 +5511,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18135</t>
+          <t>18145</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34801</t>
+          <t>33756</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5526,12 +5526,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5546,12 +5546,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11865</t>
+          <t>11612</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25271</t>
+          <t>25370</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5581,12 +5581,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>33572</t>
+          <t>33771</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>53089</t>
+          <t>55372</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,83%</t>
         </is>
       </c>
     </row>
@@ -5624,12 +5624,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>47038</t>
+          <t>46039</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67857</t>
+          <t>67046</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5639,12 +5639,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5659,12 +5659,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44019</t>
+          <t>44011</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64255</t>
+          <t>63948</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5679,7 +5679,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5694,12 +5694,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>96372</t>
+          <t>95771</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>125590</t>
+          <t>124641</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,39%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>89637</t>
+          <t>89299</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>112083</t>
+          <t>111871</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>48,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>60,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>97010</t>
+          <t>97314</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>119761</t>
+          <t>119253</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5787,47 +5787,47 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
+          <t>51,95%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>63,67%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>209684</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>193320</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>225146</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>56,17%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>51,79%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>63,94%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>296</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>209684</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>194157</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>224928</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>56,17%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>52,01%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>60,31%</t>
         </is>
       </c>
     </row>
@@ -5972,7 +5972,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4539</t>
+          <t>4408</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5987,7 +5987,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6002,12 +6002,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>696</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6202</t>
+          <t>6241</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1413</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8611</t>
+          <t>8671</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -6080,12 +6080,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>144</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5308</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6095,12 +6095,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9102</t>
+          <t>9601</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3291</t>
+          <t>2835</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12448</t>
+          <t>12093</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -6193,12 +6193,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21491</t>
+          <t>21223</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>38019</t>
+          <t>36681</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6208,12 +6208,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12245</t>
+          <t>11771</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>25598</t>
+          <t>25732</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>37093</t>
+          <t>36749</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>57927</t>
+          <t>57544</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,69%</t>
         </is>
       </c>
     </row>
@@ -6306,12 +6306,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45882</t>
+          <t>45317</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66831</t>
+          <t>65276</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6321,12 +6321,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47181</t>
+          <t>47335</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68352</t>
+          <t>69688</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>98158</t>
+          <t>97894</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>127732</t>
+          <t>127548</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>36,99%</t>
         </is>
       </c>
     </row>
@@ -6419,12 +6419,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>72737</t>
+          <t>72493</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>94178</t>
+          <t>94918</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6434,12 +6434,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,14%</t>
+          <t>55,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>80264</t>
+          <t>79659</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>102931</t>
+          <t>102499</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6469,12 +6469,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>45,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>58,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>158711</t>
+          <t>158986</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>189413</t>
+          <t>189548</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6504,12 +6504,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>54,97%</t>
         </is>
       </c>
     </row>
@@ -6649,12 +6649,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>518</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6088</t>
+          <t>5676</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6669,7 +6669,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>1424</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8481</t>
+          <t>8331</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2867</t>
+          <t>2625</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11765</t>
+          <t>11161</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -6762,12 +6762,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2477</t>
+          <t>2478</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9948</t>
+          <t>9571</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6782,7 +6782,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6194</t>
+          <t>6332</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18473</t>
+          <t>16675</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6812,12 +6812,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10126</t>
+          <t>10173</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>23278</t>
+          <t>23469</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6847,12 +6847,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -6875,12 +6875,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>42554</t>
+          <t>42507</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>64711</t>
+          <t>65067</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6890,12 +6890,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>26823</t>
+          <t>26752</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>47013</t>
+          <t>46731</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6925,12 +6925,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>74956</t>
+          <t>74868</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>103902</t>
+          <t>104570</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,56%</t>
         </is>
       </c>
     </row>
@@ -6988,12 +6988,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>97099</t>
+          <t>97561</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>126453</t>
+          <t>126715</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7003,12 +7003,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>96502</t>
+          <t>96617</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>126476</t>
+          <t>127728</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7038,12 +7038,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>201075</t>
+          <t>203354</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>243919</t>
+          <t>244731</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7073,12 +7073,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,08%</t>
         </is>
       </c>
     </row>
@@ -7101,12 +7101,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>169518</t>
+          <t>169591</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>201691</t>
+          <t>200138</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>56,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>182939</t>
+          <t>183255</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>215195</t>
+          <t>215066</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7151,12 +7151,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>361320</t>
+          <t>362627</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>407911</t>
+          <t>406179</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7186,12 +7186,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>56,56%</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse triste en 2023 (tasa de respuesta: 99,59%)</t>
+          <t>Menores según la frecuencia de sentirse triste, percibida por el adulto en 2023 (tasa de respuesta: 99,59%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7561,12 +7561,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2501</t>
+          <t>2435</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10645</t>
+          <t>11297</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1861</t>
+          <t>1895</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10935</t>
+          <t>11446</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7611,12 +7611,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6154</t>
+          <t>5964</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18396</t>
+          <t>18708</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7646,12 +7646,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -7674,12 +7674,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>392</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4997</t>
+          <t>5495</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5857</t>
+          <t>5720</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7729,7 +7729,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1235</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7962</t>
+          <t>7396</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7759,12 +7759,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -7787,12 +7787,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3655</t>
+          <t>4014</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13024</t>
+          <t>12818</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2643</t>
+          <t>2933</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11189</t>
+          <t>11626</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7837,12 +7837,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8227</t>
+          <t>8225</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21463</t>
+          <t>21335</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7877,7 +7877,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,05%</t>
         </is>
       </c>
     </row>
@@ -7900,12 +7900,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17721</t>
+          <t>17010</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36245</t>
+          <t>34522</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19343</t>
+          <t>18653</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37652</t>
+          <t>37026</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7950,12 +7950,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39560</t>
+          <t>39711</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>65770</t>
+          <t>66209</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7985,12 +7985,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,88%</t>
         </is>
       </c>
     </row>
@@ -8013,12 +8013,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>80299</t>
+          <t>80936</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>100257</t>
+          <t>100569</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8028,12 +8028,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,16%</t>
+          <t>61,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>119652</t>
+          <t>120546</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>140446</t>
+          <t>141698</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8063,12 +8063,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>70,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>206556</t>
+          <t>207192</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>236275</t>
+          <t>237427</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>78,46%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1139</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10618</t>
+          <t>10648</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2352</t>
+          <t>2088</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11855</t>
+          <t>11559</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>4951</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17718</t>
+          <t>17195</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1527</t>
+          <t>1461</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9287</t>
+          <t>8515</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1542</t>
+          <t>1738</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30930</t>
+          <t>28482</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5095</t>
+          <t>5315</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>34310</t>
+          <t>36916</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5382</t>
+          <t>5516</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17717</t>
+          <t>17831</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13874</t>
+          <t>14468</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>38109</t>
+          <t>37979</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>22721</t>
+          <t>23348</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>50334</t>
+          <t>52240</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,34%</t>
         </is>
       </c>
     </row>
@@ -8582,12 +8582,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30687</t>
+          <t>30418</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60633</t>
+          <t>59097</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8597,12 +8597,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8617,12 +8617,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>52394</t>
+          <t>51510</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>85370</t>
+          <t>84006</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8632,12 +8632,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8652,12 +8652,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>92080</t>
+          <t>90736</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>136925</t>
+          <t>135403</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8667,12 +8667,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,8%</t>
         </is>
       </c>
     </row>
@@ -8695,12 +8695,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>156472</t>
+          <t>156632</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>193496</t>
+          <t>194908</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8710,12 +8710,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8730,12 +8730,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>144411</t>
+          <t>144636</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>184620</t>
+          <t>183741</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8745,12 +8745,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>53,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>310080</t>
+          <t>308864</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>366553</t>
+          <t>366762</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8780,12 +8780,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>72,58%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4750</t>
+          <t>4680</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17101</t>
+          <t>17348</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5844</t>
+          <t>5831</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17851</t>
+          <t>18347</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13186</t>
+          <t>12902</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30956</t>
+          <t>29583</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2789</t>
+          <t>2822</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11398</t>
+          <t>11387</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9053,7 +9053,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2586</t>
+          <t>2986</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32148</t>
+          <t>37220</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7767</t>
+          <t>7983</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>37784</t>
+          <t>38816</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11487</t>
+          <t>11268</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>25810</t>
+          <t>26666</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>19769</t>
+          <t>19976</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>46137</t>
+          <t>46320</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>34921</t>
+          <t>35443</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>64178</t>
+          <t>66141</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>54850</t>
+          <t>52506</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>88053</t>
+          <t>87359</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9299,12 +9299,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>76082</t>
+          <t>76576</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>112606</t>
+          <t>112341</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9314,12 +9314,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9334,12 +9334,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>138456</t>
+          <t>138418</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>188247</t>
+          <t>189998</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9349,12 +9349,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,52%</t>
         </is>
       </c>
     </row>
@@ -9377,12 +9377,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>244233</t>
+          <t>245503</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>286605</t>
+          <t>288172</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9392,12 +9392,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9412,12 +9412,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>274669</t>
+          <t>272431</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>319783</t>
+          <t>316742</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>72,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>530478</t>
+          <t>531507</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>591721</t>
+          <t>592532</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>73,34%</t>
         </is>
       </c>
     </row>
